--- a/data/trans_dic/P44-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P44-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se ha realizado alguna vez una prueba para detectar el cancer de colon</t>
+          <t>Población que se ha realizado alguna vez una prueba para detectar el cancer de colon (tasa de respuesta: 98,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,26; 23,5</t>
+          <t>8,36; 22,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,27; 25,33</t>
+          <t>12,19; 24,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46,56; 57,58</t>
+          <t>45,18; 56,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,29; 37,29</t>
+          <t>12,79; 37,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,54; 17,68</t>
+          <t>4,56; 18,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,1; 47,72</t>
+          <t>36,48; 47,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,52; 23,51</t>
+          <t>12,07; 23,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,61; 20,4</t>
+          <t>10,57; 19,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>43,43; 51,6</t>
+          <t>43,46; 51,33</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,5; 17,43</t>
+          <t>6,31; 16,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,71; 26,41</t>
+          <t>13,12; 26,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,1; 43,76</t>
+          <t>31,74; 43,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,79; 24,46</t>
+          <t>4,86; 23,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 11,94</t>
+          <t>2,19; 12,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,33; 41,21</t>
+          <t>29,65; 41,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,26; 17,16</t>
+          <t>7,61; 16,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,3; 18,76</t>
+          <t>9,43; 19,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32,65; 41,0</t>
+          <t>32,22; 40,64</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,4; 17,0</t>
+          <t>7,22; 16,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,68; 15,59</t>
+          <t>7,66; 15,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37,77; 90,97</t>
+          <t>38,22; 91,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,68; 17,41</t>
+          <t>4,34; 16,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,85; 17,16</t>
+          <t>3,92; 18,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,82; 39,93</t>
+          <t>25,79; 39,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,45; 14,72</t>
+          <t>7,49; 14,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,43; 14,68</t>
+          <t>7,84; 14,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36,03; 88,48</t>
+          <t>35,86; 87,01</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,9; 11,77</t>
+          <t>6,03; 11,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,53; 12,81</t>
+          <t>7,4; 12,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,06; 35,63</t>
+          <t>27,91; 35,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,65; 12,65</t>
+          <t>4,6; 12,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,85; 14,18</t>
+          <t>6,05; 14,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,82; 30,37</t>
+          <t>5,94; 29,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,31; 10,98</t>
+          <t>6,3; 11,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,75; 12,12</t>
+          <t>7,71; 11,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,39; 31,57</t>
+          <t>12,35; 31,48</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,23; 8,79</t>
+          <t>2,29; 9,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,31; 12,88</t>
+          <t>6,39; 12,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24,19; 34,74</t>
+          <t>23,68; 34,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,92; 11,14</t>
+          <t>5,0; 10,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,15; 11,03</t>
+          <t>5,29; 11,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,23; 29,42</t>
+          <t>23,12; 29,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,67; 8,96</t>
+          <t>4,66; 9,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,19; 10,57</t>
+          <t>6,4; 10,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24,32; 29,91</t>
+          <t>24,42; 29,8</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,75; 58,27</t>
+          <t>13,15; 62,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,7; 7,14</t>
+          <t>3,71; 7,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,31; 8,46</t>
+          <t>4,15; 8,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,27; 30,26</t>
+          <t>24,32; 30,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,46; 7,12</t>
+          <t>3,57; 7,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,31; 8,16</t>
+          <t>4,3; 8,25</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24,64; 30,63</t>
+          <t>24,59; 30,92</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,77; 11,58</t>
+          <t>7,7; 11,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,15; 13,55</t>
+          <t>10,22; 13,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35,85; 67,25</t>
+          <t>35,9; 65,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,18; 9,05</t>
+          <t>6,12; 8,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,01; 8,83</t>
+          <t>6,15; 8,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,44; 30,62</t>
+          <t>18,23; 30,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,27; 9,69</t>
+          <t>7,19; 9,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,46; 10,6</t>
+          <t>8,37; 10,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>29,76; 50,98</t>
+          <t>29,95; 51,98</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se ha realizado alguna vez una prueba para detectar el cancer de colon</t>
+          <t>Población que se ha realizado alguna vez una prueba para detectar el cancer de colon (tasa de respuesta: 98,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12948; 32859</t>
+          <t>11684; 31256</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>21238; 43835</t>
+          <t>21097; 42494</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>116996; 144694</t>
+          <t>113547; 142165</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7629; 21414</t>
+          <t>7342; 21432</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4967; 19333</t>
+          <t>4985; 19814</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>63221; 83579</t>
+          <t>63894; 83324</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22732; 46379</t>
+          <t>23809; 46162</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>29957; 57603</t>
+          <t>29861; 56059</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>185217; 220051</t>
+          <t>185344; 218889</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9539; 25566</t>
+          <t>9257; 24920</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18239; 37887</t>
+          <t>18827; 37298</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>70661; 96326</t>
+          <t>69855; 96153</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3931; 16607</t>
+          <t>3299; 15857</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2117; 11476</t>
+          <t>2101; 12071</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41261; 57976</t>
+          <t>41713; 58206</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15571; 36814</t>
+          <t>16321; 35943</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22273; 44932</t>
+          <t>22585; 45876</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>117793; 147934</t>
+          <t>116245; 146607</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18965; 43577</t>
+          <t>18518; 42611</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20571; 41731</t>
+          <t>20510; 42071</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>173714; 418336</t>
+          <t>175766; 421855</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5533; 20591</t>
+          <t>5139; 19865</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3132; 13973</t>
+          <t>3192; 14727</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25835; 39961</t>
+          <t>25811; 39195</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27900; 55154</t>
+          <t>28057; 54989</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25937; 51267</t>
+          <t>27376; 51618</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>201745; 495430</t>
+          <t>200799; 487200</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26955; 53834</t>
+          <t>27561; 52559</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40253; 68495</t>
+          <t>39569; 66227</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>142462; 180898</t>
+          <t>141685; 180430</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9129; 24824</t>
+          <t>9032; 23790</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14979; 36297</t>
+          <t>15478; 36502</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29122; 151840</t>
+          <t>29684; 149136</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>41235; 71737</t>
+          <t>41144; 72225</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>61295; 95811</t>
+          <t>60941; 94016</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>124828; 318120</t>
+          <t>124408; 317244</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4231; 16692</t>
+          <t>4347; 18038</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>17217; 35133</t>
+          <t>17439; 35231</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>56506; 81148</t>
+          <t>55306; 79419</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17671; 39994</t>
+          <t>17960; 38593</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>19645; 42062</t>
+          <t>20182; 42748</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>98516; 124747</t>
+          <t>98034; 124710</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25643; 49191</t>
+          <t>25589; 51153</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>40492; 69130</t>
+          <t>41851; 71098</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>159945; 196721</t>
+          <t>160583; 195935</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1463</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1744</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1576; 6676</t>
+          <t>1507; 7193</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24569; 47381</t>
+          <t>24629; 48511</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>28511; 55990</t>
+          <t>27448; 53421</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>107024; 133419</t>
+          <t>107219; 134327</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23118; 47548</t>
+          <t>23847; 46814</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>28767; 54430</t>
+          <t>28706; 55062</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>111479; 138560</t>
+          <t>111248; 139862</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>92764; 138282</t>
+          <t>91941; 138120</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>141757; 189267</t>
+          <t>142753; 190301</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>603748; 1132541</t>
+          <t>604527; 1099495</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>90348; 132333</t>
+          <t>89432; 129108</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>95309; 140067</t>
+          <t>97571; 141337</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>292847; 545367</t>
+          <t>324640; 543936</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>193009; 257516</t>
+          <t>190883; 253852</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>252502; 316205</t>
+          <t>249531; 318911</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1031074; 1766515</t>
+          <t>1037566; 1800881</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P44-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P44-Clase-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,4%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,36; 22,35</t>
+          <t>8,36; 22,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,19; 24,56</t>
+          <t>12,1; 25,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45,18; 56,57</t>
+          <t>44,95; 56,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,79; 37,32</t>
+          <t>12,7; 37,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,56; 18,12</t>
+          <t>4,75; 18,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,48; 47,58</t>
+          <t>37,41; 48,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,07; 23,4</t>
+          <t>11,24; 23,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,57; 19,85</t>
+          <t>10,63; 19,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>43,46; 51,33</t>
+          <t>43,6; 51,59</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>35,62%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,31; 16,99</t>
+          <t>6,49; 17,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,12; 26,0</t>
+          <t>12,7; 26,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31,74; 43,69</t>
+          <t>30,93; 42,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,86; 23,35</t>
+          <t>4,86; 22,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 12,56</t>
+          <t>2,13; 12,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,65; 41,38</t>
+          <t>28,85; 40,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,61; 16,75</t>
+          <t>7,47; 16,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,43; 19,15</t>
+          <t>9,37; 18,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32,22; 40,64</t>
+          <t>31,26; 39,95</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>36,7%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,22; 16,62</t>
+          <t>7,5; 16,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,66; 15,72</t>
+          <t>7,68; 16,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38,22; 91,73</t>
+          <t>32,8; 44,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,34; 16,79</t>
+          <t>4,79; 16,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 18,08</t>
+          <t>3,87; 16,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,79; 39,17</t>
+          <t>25,75; 39,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,49; 14,68</t>
+          <t>7,43; 14,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,84; 14,78</t>
+          <t>7,74; 14,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>35,86; 87,01</t>
+          <t>32,42; 41,66</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>30,86%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,03; 11,5</t>
+          <t>5,95; 11,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,4; 12,39</t>
+          <t>7,39; 12,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,91; 35,54</t>
+          <t>28,73; 36,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 12,12</t>
+          <t>4,76; 12,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,05; 14,26</t>
+          <t>6,07; 14,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,94; 29,83</t>
+          <t>25,42; 32,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,3; 11,05</t>
+          <t>6,11; 10,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,71; 11,89</t>
+          <t>7,74; 12,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,35; 31,48</t>
+          <t>27,92; 33,38</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,23%</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,29; 9,5</t>
+          <t>2,71; 9,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,39; 12,91</t>
+          <t>6,12; 12,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23,68; 34,0</t>
+          <t>23,35; 34,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,0; 10,75</t>
+          <t>4,87; 10,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,29; 11,21</t>
+          <t>5,06; 11,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,12; 29,41</t>
+          <t>23,33; 29,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,66; 9,32</t>
+          <t>4,78; 9,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,4; 10,87</t>
+          <t>6,39; 10,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24,42; 29,8</t>
+          <t>24,58; 30,04</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>28,18%</t>
         </is>
       </c>
     </row>
@@ -1238,37 +1238,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,15; 62,78</t>
+          <t>11,68; 63,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,71; 7,31</t>
+          <t>3,62; 6,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,15; 8,07</t>
+          <t>4,44; 8,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,32; 30,46</t>
+          <t>25,18; 31,68</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,57; 7,01</t>
+          <t>3,52; 7,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,3; 8,25</t>
+          <t>4,23; 8,15</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24,59; 30,92</t>
+          <t>24,98; 31,26</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>33,21%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,7; 11,57</t>
+          <t>7,78; 11,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,22; 13,62</t>
+          <t>10,13; 13,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35,9; 65,29</t>
+          <t>33,91; 38,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,12; 8,83</t>
+          <t>6,12; 9,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,15; 8,91</t>
+          <t>6,12; 9,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,23; 30,54</t>
+          <t>28,76; 32,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,19; 9,56</t>
+          <t>7,19; 9,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,37; 10,69</t>
+          <t>8,45; 10,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>29,95; 51,98</t>
+          <t>31,82; 34,55</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>129190</t>
+          <t>137732</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73662</t>
+          <t>83088</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>202853</t>
+          <t>220820</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11684; 31256</t>
+          <t>11690; 31882</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>21097; 42494</t>
+          <t>20938; 43612</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>113547; 142165</t>
+          <t>121935; 152124</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7342; 21432</t>
+          <t>7292; 21392</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4985; 19814</t>
+          <t>5195; 19820</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>63894; 83324</t>
+          <t>72789; 94181</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23809; 46162</t>
+          <t>22165; 46874</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>29861; 56059</t>
+          <t>30023; 55951</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>185344; 218889</t>
+          <t>203128; 240342</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>82796</t>
+          <t>85974</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49547</t>
+          <t>55523</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>132342</t>
+          <t>141497</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9257; 24920</t>
+          <t>9524; 25893</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18827; 37298</t>
+          <t>18214; 38200</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69855; 96153</t>
+          <t>73507; 100681</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3299; 15857</t>
+          <t>3299; 15006</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2101; 12071</t>
+          <t>2049; 11759</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41713; 58206</t>
+          <t>46030; 64530</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16321; 35943</t>
+          <t>16027; 36343</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22585; 45876</t>
+          <t>22442; 44181</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>116245; 146607</t>
+          <t>124153; 158682</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>330058</t>
+          <t>91438</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32589</t>
+          <t>36020</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>362648</t>
+          <t>127458</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18518; 42611</t>
+          <t>19221; 43091</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20510; 42071</t>
+          <t>20569; 43005</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>175766; 421855</t>
+          <t>77849; 104932</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5139; 19865</t>
+          <t>5667; 19925</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3192; 14727</t>
+          <t>3156; 13800</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25811; 39195</t>
+          <t>28308; 43691</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28057; 54989</t>
+          <t>27820; 55077</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27376; 51618</t>
+          <t>27011; 50131</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>200799; 487200</t>
+          <t>112566; 144675</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>160943</t>
+          <t>175722</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85493</t>
+          <t>93522</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>246436</t>
+          <t>269243</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27561; 52559</t>
+          <t>27207; 52563</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>39569; 66227</t>
+          <t>39487; 67113</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>141685; 180430</t>
+          <t>157319; 197239</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9032; 23790</t>
+          <t>9335; 24401</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15478; 36502</t>
+          <t>15530; 36011</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29684; 149136</t>
+          <t>82586; 106839</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>41144; 72225</t>
+          <t>39934; 69555</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>60941; 94016</t>
+          <t>61168; 94878</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>124408; 317244</t>
+          <t>243598; 291209</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>67607</t>
+          <t>74345</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>110987</t>
+          <t>120620</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>178594</t>
+          <t>194965</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4347; 18038</t>
+          <t>5152; 17173</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>17439; 35231</t>
+          <t>16697; 34427</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>55306; 79419</t>
+          <t>60489; 88616</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17960; 38593</t>
+          <t>17501; 37544</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>20182; 42748</t>
+          <t>19305; 42282</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>98034; 124710</t>
+          <t>106635; 133812</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25589; 51153</t>
+          <t>26266; 50257</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>41851; 71098</t>
+          <t>41767; 69886</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>160583; 195935</t>
+          <t>176031; 215126</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>120382</t>
+          <t>132881</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>124268</t>
+          <t>136730</t>
         </is>
       </c>
     </row>
@@ -2464,37 +2464,37 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1507; 7193</t>
+          <t>1338; 7288</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24629; 48511</t>
+          <t>23998; 46229</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>27448; 53421</t>
+          <t>29369; 54946</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>107219; 134327</t>
+          <t>119287; 150105</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23847; 46814</t>
+          <t>23474; 47050</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>28706; 55062</t>
+          <t>28251; 54406</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>111248; 139862</t>
+          <t>121198; 151688</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>774479</t>
+          <t>569060</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>472662</t>
+          <t>521654</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1247141</t>
+          <t>1090714</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>91941; 138120</t>
+          <t>92930; 136953</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>142753; 190301</t>
+          <t>141500; 191255</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>604527; 1099495</t>
+          <t>530548; 604812</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>89432; 129108</t>
+          <t>89461; 131536</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>97571; 141337</t>
+          <t>97055; 143204</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>324640; 543936</t>
+          <t>494548; 550891</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>190883; 253852</t>
+          <t>190928; 254240</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>249531; 318911</t>
+          <t>252196; 318135</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1037566; 1800881</t>
+          <t>1045119; 1134752</t>
         </is>
       </c>
     </row>
